--- a/data/nzd0604/nzd0604.xlsx
+++ b/data/nzd0604/nzd0604.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M362"/>
+  <dimension ref="A1:M365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16516,22 +16516,22 @@
         <v>227.7</v>
       </c>
       <c r="G360" t="n">
-        <v>291.05</v>
+        <v>263.66</v>
       </c>
       <c r="H360" t="n">
         <v>296.21</v>
       </c>
       <c r="I360" t="n">
-        <v>373.07</v>
+        <v>359.11</v>
       </c>
       <c r="J360" t="n">
-        <v>370.17</v>
+        <v>257.34</v>
       </c>
       <c r="K360" t="n">
         <v>361.59</v>
       </c>
       <c r="L360" t="n">
-        <v>310.55</v>
+        <v>302.92</v>
       </c>
       <c r="M360" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>301.97</v>
       </c>
       <c r="C361" t="n">
-        <v>271.01</v>
+        <v>256.11</v>
       </c>
       <c r="D361" t="n">
         <v>234.41</v>
@@ -16561,22 +16561,22 @@
         <v>225.08</v>
       </c>
       <c r="G361" t="n">
-        <v>316.1</v>
+        <v>261.41</v>
       </c>
       <c r="H361" t="n">
         <v>296.21</v>
       </c>
       <c r="I361" t="n">
-        <v>383.64</v>
+        <v>359.11</v>
       </c>
       <c r="J361" t="n">
-        <v>407.76</v>
+        <v>257.34</v>
       </c>
       <c r="K361" t="n">
         <v>360.83</v>
       </c>
       <c r="L361" t="n">
-        <v>312.5</v>
+        <v>297.76</v>
       </c>
       <c r="M361" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>305.1</v>
       </c>
       <c r="C362" t="n">
-        <v>285.37</v>
+        <v>253.48</v>
       </c>
       <c r="D362" t="n">
         <v>231.59</v>
@@ -16606,24 +16606,159 @@
         <v>222.95</v>
       </c>
       <c r="G362" t="n">
-        <v>337.51</v>
+        <v>259.71</v>
       </c>
       <c r="H362" t="n">
-        <v>315.8</v>
+        <v>295.14</v>
       </c>
       <c r="I362" t="n">
-        <v>388.68</v>
+        <v>361.75</v>
       </c>
       <c r="J362" t="n">
-        <v>407.76</v>
+        <v>257.34</v>
       </c>
       <c r="K362" t="n">
-        <v>381.92</v>
+        <v>364.2</v>
       </c>
       <c r="L362" t="n">
-        <v>313.67</v>
+        <v>294.79</v>
       </c>
       <c r="M362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>305.1</v>
+      </c>
+      <c r="C363" t="n">
+        <v>253.17</v>
+      </c>
+      <c r="D363" t="n">
+        <v>231.63</v>
+      </c>
+      <c r="E363" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="F363" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="G363" t="n">
+        <v>257.96</v>
+      </c>
+      <c r="H363" t="n">
+        <v>291.96</v>
+      </c>
+      <c r="I363" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="J363" t="n">
+        <v>267.57</v>
+      </c>
+      <c r="K363" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="L363" t="n">
+        <v>290.6</v>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>305.1</v>
+      </c>
+      <c r="C364" t="n">
+        <v>251.25</v>
+      </c>
+      <c r="D364" t="n">
+        <v>232.69</v>
+      </c>
+      <c r="E364" t="n">
+        <v>236.99</v>
+      </c>
+      <c r="F364" t="n">
+        <v>224.81</v>
+      </c>
+      <c r="G364" t="n">
+        <v>267.16</v>
+      </c>
+      <c r="H364" t="n">
+        <v>296.37</v>
+      </c>
+      <c r="I364" t="n">
+        <v>355.52</v>
+      </c>
+      <c r="J364" t="n">
+        <v>291.04</v>
+      </c>
+      <c r="K364" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="L364" t="n">
+        <v>284.15</v>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>305.75</v>
+      </c>
+      <c r="C365" t="n">
+        <v>250.83</v>
+      </c>
+      <c r="D365" t="n">
+        <v>234.7</v>
+      </c>
+      <c r="E365" t="n">
+        <v>239.54</v>
+      </c>
+      <c r="F365" t="n">
+        <v>226.9</v>
+      </c>
+      <c r="G365" t="n">
+        <v>274.91</v>
+      </c>
+      <c r="H365" t="n">
+        <v>296.37</v>
+      </c>
+      <c r="I365" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="J365" t="n">
+        <v>309.68</v>
+      </c>
+      <c r="K365" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="L365" t="n">
+        <v>284.15</v>
+      </c>
+      <c r="M365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16640,7 +16775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B395"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20593,6 +20728,36 @@
       </c>
       <c r="B395" t="n">
         <v>-0.97</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -20755,28 +20920,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7166822241467752</v>
+        <v>0.7151911056085356</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1401098389054164</v>
+        <v>0.1415635015635255</v>
       </c>
       <c r="M2" t="n">
-        <v>9.755158616596411</v>
+        <v>9.682317299019767</v>
       </c>
       <c r="N2" t="n">
-        <v>177.6754699731193</v>
+        <v>176.2195251672947</v>
       </c>
       <c r="O2" t="n">
-        <v>13.32949623853502</v>
+        <v>13.27477024913406</v>
       </c>
       <c r="P2" t="n">
-        <v>287.2939722755952</v>
+        <v>287.3097900491392</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20827,28 +20992,28 @@
         <v>0.0364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2631513577114719</v>
+        <v>0.2378423361241283</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03383409514353775</v>
+        <v>0.0292359687825825</v>
       </c>
       <c r="M3" t="n">
-        <v>7.828651879900448</v>
+        <v>7.639139619072402</v>
       </c>
       <c r="N3" t="n">
-        <v>111.4470437150247</v>
+        <v>106.7012968517212</v>
       </c>
       <c r="O3" t="n">
-        <v>10.55684819039398</v>
+        <v>10.32963198045899</v>
       </c>
       <c r="P3" t="n">
-        <v>245.9008140929363</v>
+        <v>246.168776871908</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20899,28 +21064,28 @@
         <v>0.0694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3891081323054241</v>
+        <v>0.3821776977939558</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08984296521093404</v>
+        <v>0.08807327233923112</v>
       </c>
       <c r="M4" t="n">
-        <v>6.870875503838646</v>
+        <v>6.838452935504402</v>
       </c>
       <c r="N4" t="n">
-        <v>86.4436406958219</v>
+        <v>85.9095964201363</v>
       </c>
       <c r="O4" t="n">
-        <v>9.297507230210789</v>
+        <v>9.268742979505705</v>
       </c>
       <c r="P4" t="n">
-        <v>227.2416397146459</v>
+        <v>227.3152292287192</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20971,28 +21136,28 @@
         <v>0.1048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2025161634178604</v>
+        <v>0.2098112308841171</v>
       </c>
       <c r="J5" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03144489411089202</v>
+        <v>0.03411052792680658</v>
       </c>
       <c r="M5" t="n">
-        <v>6.398390288584366</v>
+        <v>6.379769132176558</v>
       </c>
       <c r="N5" t="n">
-        <v>71.19569962718369</v>
+        <v>70.80951857597891</v>
       </c>
       <c r="O5" t="n">
-        <v>8.437754418515846</v>
+        <v>8.41483918895536</v>
       </c>
       <c r="P5" t="n">
-        <v>227.3842480150259</v>
+        <v>227.3067319762747</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21043,28 +21208,28 @@
         <v>0.0842</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3874133049804891</v>
+        <v>0.3872846686042968</v>
       </c>
       <c r="J6" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1089804216006243</v>
+        <v>0.1104735410772875</v>
       </c>
       <c r="M6" t="n">
-        <v>6.262682399031624</v>
+        <v>6.221703311947952</v>
       </c>
       <c r="N6" t="n">
-        <v>69.15888897813402</v>
+        <v>68.60509857932179</v>
       </c>
       <c r="O6" t="n">
-        <v>8.316182355993284</v>
+        <v>8.282819482478281</v>
       </c>
       <c r="P6" t="n">
-        <v>214.8170319311224</v>
+        <v>214.8183680069727</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21115,28 +21280,28 @@
         <v>0.0299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6058918736595098</v>
+        <v>0.5510120400123901</v>
       </c>
       <c r="J7" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K7" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02706567238118696</v>
+        <v>0.02393449512984758</v>
       </c>
       <c r="M7" t="n">
-        <v>20.3531338334902</v>
+        <v>19.93530973536277</v>
       </c>
       <c r="N7" t="n">
-        <v>745.1741927935499</v>
+        <v>704.7145707353967</v>
       </c>
       <c r="O7" t="n">
-        <v>27.2978789064929</v>
+        <v>26.54646060655538</v>
       </c>
       <c r="P7" t="n">
-        <v>233.8589494304905</v>
+        <v>234.4372016265926</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21187,28 +21352,28 @@
         <v>0.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>1.515826127209858</v>
+        <v>1.456906975305248</v>
       </c>
       <c r="J8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K8" t="n">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09030774499599592</v>
+        <v>0.08462501320973281</v>
       </c>
       <c r="M8" t="n">
-        <v>27.00909604598472</v>
+        <v>26.98540316257864</v>
       </c>
       <c r="N8" t="n">
-        <v>1269.980875505599</v>
+        <v>1269.292377341219</v>
       </c>
       <c r="O8" t="n">
-        <v>35.63679103827391</v>
+        <v>35.62712979375716</v>
       </c>
       <c r="P8" t="n">
-        <v>285.4205768217528</v>
+        <v>286.064513529681</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21259,28 +21424,28 @@
         <v>0.0114</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06474695759258531</v>
+        <v>-0.06416754688195825</v>
       </c>
       <c r="J9" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K9" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004604039560601736</v>
+        <v>0.0004692776972826662</v>
       </c>
       <c r="M9" t="n">
-        <v>17.15451616624139</v>
+        <v>17.01276180748278</v>
       </c>
       <c r="N9" t="n">
-        <v>500.6672342741655</v>
+        <v>486.3419403478482</v>
       </c>
       <c r="O9" t="n">
-        <v>22.37559461275086</v>
+        <v>22.05316168597709</v>
       </c>
       <c r="P9" t="n">
-        <v>334.7284012857733</v>
+        <v>334.720469215685</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21331,28 +21496,28 @@
         <v>0.0157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5613641325990605</v>
+        <v>0.3244002402351487</v>
       </c>
       <c r="J10" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K10" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0338974956967889</v>
+        <v>0.01326496794598031</v>
       </c>
       <c r="M10" t="n">
-        <v>15.65976110633746</v>
+        <v>15.38056538005561</v>
       </c>
       <c r="N10" t="n">
-        <v>494.9051383104223</v>
+        <v>434.823373762459</v>
       </c>
       <c r="O10" t="n">
-        <v>22.24646350120446</v>
+        <v>20.85241889475796</v>
       </c>
       <c r="P10" t="n">
-        <v>288.8390639221827</v>
+        <v>291.3895094540683</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21403,28 +21568,28 @@
         <v>0.0103</v>
       </c>
       <c r="I11" t="n">
-        <v>3.624594115845101</v>
+        <v>3.581059591551641</v>
       </c>
       <c r="J11" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K11" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3274640656299713</v>
+        <v>0.3249729124002909</v>
       </c>
       <c r="M11" t="n">
-        <v>31.19913297705519</v>
+        <v>31.10184933287506</v>
       </c>
       <c r="N11" t="n">
-        <v>1462.148253250897</v>
+        <v>1455.04809702444</v>
       </c>
       <c r="O11" t="n">
-        <v>38.2380471945273</v>
+        <v>38.14509269911976</v>
       </c>
       <c r="P11" t="n">
-        <v>294.4981813726746</v>
+        <v>294.9762091663259</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21475,28 +21640,28 @@
         <v>0.0174</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1517184854375234</v>
+        <v>-0.1772893591757536</v>
       </c>
       <c r="J12" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002910344339937421</v>
+        <v>0.004065757625929312</v>
       </c>
       <c r="M12" t="n">
-        <v>15.05737777059242</v>
+        <v>14.89783135499654</v>
       </c>
       <c r="N12" t="n">
-        <v>446.3817586155558</v>
+        <v>439.247470309985</v>
       </c>
       <c r="O12" t="n">
-        <v>21.12774854582371</v>
+        <v>20.95823156447092</v>
       </c>
       <c r="P12" t="n">
-        <v>293.4993301182338</v>
+        <v>293.7694202230308</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21534,7 +21699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M362"/>
+  <dimension ref="A1:M365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45395,7 +45560,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>-36.94675576105797,175.16932678069026</t>
+          <t>-36.94698001791882,175.1694551512696</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -45405,12 +45570,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>-36.94547932383964,175.17054434409945</t>
+          <t>-36.94559291615708,175.17061165110908</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>-36.945287233789074,175.17079806413383</t>
+          <t>-36.94604621194875,175.171640767646</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
@@ -45420,7 +45585,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>-36.94502014885427,175.17137595620324</t>
+          <t>-36.94502746742775,175.17146112177625</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -45442,7 +45607,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>-36.947567885093186,175.16630429913957</t>
+          <t>-36.94770208936071,175.16630888008797</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -45462,7 +45627,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>-36.946550662902844,175.16920937783064</t>
+          <t>-36.946998439887714,175.16946569653257</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -45472,12 +45637,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>-36.94539331587196,175.1704933818378</t>
+          <t>-36.94559291615708,175.17061165110908</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>-36.94508657400616,175.17057527295486</t>
+          <t>-36.94604621194875,175.171640767646</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
@@ -45487,7 +45652,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>-36.94501827843569,175.17135419042984</t>
+          <t>-36.945032416781956,175.1715187173744</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -45509,7 +45674,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>-36.94743854460117,175.16629988423853</t>
+          <t>-36.94772577776462,175.1663096886744</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -45529,35 +45694,236 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>-36.94637536732024,175.16910903522458</t>
+          <t>-36.947012358707916,175.16947366406805</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>-36.946254890187205,175.1700094294443</t>
+          <t>-36.94642300072488,175.17010903997743</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>-36.94535230544085,175.17046908199313</t>
+          <t>-36.945571434518975,175.17059892254701</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>-36.94508657400616,175.17057527295486</t>
+          <t>-36.94604621194875,175.171640767646</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>-36.94551369709672,175.17049692719692</t>
+          <t>-36.94554556874309,175.17069184491032</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>-36.9450171561826,175.17134113096623</t>
+          <t>-36.94503526552536,175.1715518683319</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-36.94712868088998,175.1658211035412</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-36.94772856993388,175.1663097839831</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-36.947875556114155,175.1671843906084</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-36.94776061503204,175.16807275956577</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-36.94761117576448,175.16882810351893</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-36.94702668690448,175.16948186594595</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-36.946448876393916,175.17012437213262</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-36.94563653038691,175.17063749396993</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-36.945977397663626,175.171564361237</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-36.94554556874309,175.17069184491032</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-36.94503928444378,175.17159863685785</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-36.94712868088998,175.1658211035412</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-36.947745863369356,175.16631037428255</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-36.9478660575206,175.16718314578404</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-36.94775263901736,175.16807172370554</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-36.947598812538246,175.16882102651473</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-36.94695136152042,175.1694387475377</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-36.94641299221073,175.1701031096184</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-36.94562212792744,175.17062896003677</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-36.94581952147836,175.17138906768113</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-36.94553803253105,175.17064575543773</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-36.94504547104793,175.17167063137464</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-36.94712310041685,175.16582331823855</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-36.94774964630837,175.1663105034106</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-36.94784804603652,175.16718078531616</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-36.947729786390866,175.16806875579283</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-36.94758170052224,175.1688112311949</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-36.94688790805692,175.1694024250337</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-36.94641299221073,175.1701031096184</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-36.94562082601017,175.17062818860794</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-36.94569413516042,175.1712498491163</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-36.945523625545185,175.17055764646886</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-36.94504547104793,175.17167063137464</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0604/nzd0604.xlsx
+++ b/data/nzd0604/nzd0604.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M365"/>
+  <dimension ref="A1:M367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16699,13 +16699,13 @@
         <v>267.16</v>
       </c>
       <c r="H364" t="n">
-        <v>296.37</v>
+        <v>291.32</v>
       </c>
       <c r="I364" t="n">
-        <v>355.52</v>
+        <v>353.75</v>
       </c>
       <c r="J364" t="n">
-        <v>291.04</v>
+        <v>267.57</v>
       </c>
       <c r="K364" t="n">
         <v>368.39</v>
@@ -16744,13 +16744,13 @@
         <v>274.91</v>
       </c>
       <c r="H365" t="n">
-        <v>296.37</v>
+        <v>291.32</v>
       </c>
       <c r="I365" t="n">
-        <v>355.68</v>
+        <v>353.75</v>
       </c>
       <c r="J365" t="n">
-        <v>309.68</v>
+        <v>267.57</v>
       </c>
       <c r="K365" t="n">
         <v>376.4</v>
@@ -16759,6 +16759,96 @@
         <v>284.15</v>
       </c>
       <c r="M365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>306.68</v>
+      </c>
+      <c r="C366" t="n">
+        <v>251.37</v>
+      </c>
+      <c r="D366" t="n">
+        <v>236.02</v>
+      </c>
+      <c r="E366" t="n">
+        <v>241.34</v>
+      </c>
+      <c r="F366" t="n">
+        <v>228.35</v>
+      </c>
+      <c r="G366" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="H366" t="n">
+        <v>291.32</v>
+      </c>
+      <c r="I366" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="J366" t="n">
+        <v>267.57</v>
+      </c>
+      <c r="K366" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="L366" t="n">
+        <v>284.15</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>307.79</v>
+      </c>
+      <c r="C367" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="D367" t="n">
+        <v>237.31</v>
+      </c>
+      <c r="E367" t="n">
+        <v>242.57</v>
+      </c>
+      <c r="F367" t="n">
+        <v>229.58</v>
+      </c>
+      <c r="G367" t="n">
+        <v>268.24</v>
+      </c>
+      <c r="H367" t="n">
+        <v>286.53</v>
+      </c>
+      <c r="I367" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="J367" t="n">
+        <v>265.27</v>
+      </c>
+      <c r="K367" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="L367" t="n">
+        <v>282.84</v>
+      </c>
+      <c r="M367" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16775,7 +16865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B398"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20758,6 +20848,26 @@
       </c>
       <c r="B398" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -20920,28 +21030,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7151911056085356</v>
+        <v>0.7161011603746089</v>
       </c>
       <c r="J2" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K2" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1415635015635255</v>
+        <v>0.1431759777813371</v>
       </c>
       <c r="M2" t="n">
-        <v>9.682317299019767</v>
+        <v>9.634578410877445</v>
       </c>
       <c r="N2" t="n">
-        <v>176.2195251672947</v>
+        <v>175.2625064345506</v>
       </c>
       <c r="O2" t="n">
-        <v>13.27477024913406</v>
+        <v>13.23867464796044</v>
       </c>
       <c r="P2" t="n">
-        <v>287.3097900491392</v>
+        <v>287.3000852366188</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20992,28 +21102,28 @@
         <v>0.0364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2378423361241283</v>
+        <v>0.2361170371214275</v>
       </c>
       <c r="J3" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K3" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0292359687825825</v>
+        <v>0.02912143960234859</v>
       </c>
       <c r="M3" t="n">
-        <v>7.639139619072402</v>
+        <v>7.606263313465289</v>
       </c>
       <c r="N3" t="n">
-        <v>106.7012968517212</v>
+        <v>106.1343351721279</v>
       </c>
       <c r="O3" t="n">
-        <v>10.32963198045899</v>
+        <v>10.30215196801755</v>
       </c>
       <c r="P3" t="n">
-        <v>246.168776871908</v>
+        <v>246.1871875669279</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21064,28 +21174,28 @@
         <v>0.0694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3821776977939558</v>
+        <v>0.3813566166722216</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08807327233923112</v>
+        <v>0.08858179190107007</v>
       </c>
       <c r="M4" t="n">
-        <v>6.838452935504402</v>
+        <v>6.803827160484137</v>
       </c>
       <c r="N4" t="n">
-        <v>85.9095964201363</v>
+        <v>85.44467351516258</v>
       </c>
       <c r="O4" t="n">
-        <v>9.268742979505705</v>
+        <v>9.243628806651778</v>
       </c>
       <c r="P4" t="n">
-        <v>227.3152292287192</v>
+        <v>227.3239752734137</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21136,28 +21246,28 @@
         <v>0.1048</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2098112308841171</v>
+        <v>0.2189445045845074</v>
       </c>
       <c r="J5" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K5" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03411052792680658</v>
+        <v>0.03718908890736783</v>
       </c>
       <c r="M5" t="n">
-        <v>6.379769132176558</v>
+        <v>6.387552826198422</v>
       </c>
       <c r="N5" t="n">
-        <v>70.80951857597891</v>
+        <v>70.86678752760209</v>
       </c>
       <c r="O5" t="n">
-        <v>8.41483918895536</v>
+        <v>8.418241355984163</v>
       </c>
       <c r="P5" t="n">
-        <v>227.3067319762747</v>
+        <v>227.2093139070572</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21208,28 +21318,28 @@
         <v>0.0842</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3872846686042968</v>
+        <v>0.3911571512982492</v>
       </c>
       <c r="J6" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K6" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104735410772875</v>
+        <v>0.1133946554450329</v>
       </c>
       <c r="M6" t="n">
-        <v>6.221703311947952</v>
+        <v>6.20375368548447</v>
       </c>
       <c r="N6" t="n">
-        <v>68.60509857932179</v>
+        <v>68.31081894657788</v>
       </c>
       <c r="O6" t="n">
-        <v>8.282819482478281</v>
+        <v>8.265035931354314</v>
       </c>
       <c r="P6" t="n">
-        <v>214.8183680069727</v>
+        <v>214.7770570687182</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21280,28 +21390,28 @@
         <v>0.0299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5510120400123901</v>
+        <v>0.5725074089130167</v>
       </c>
       <c r="J7" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K7" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02393449512984758</v>
+        <v>0.02596907863902886</v>
       </c>
       <c r="M7" t="n">
-        <v>19.93530973536277</v>
+        <v>19.92093248500047</v>
       </c>
       <c r="N7" t="n">
-        <v>704.7145707353967</v>
+        <v>703.3439925896243</v>
       </c>
       <c r="O7" t="n">
-        <v>26.54646060655538</v>
+        <v>26.52063333688742</v>
       </c>
       <c r="P7" t="n">
-        <v>234.4372016265926</v>
+        <v>234.2083086554561</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21352,28 +21462,28 @@
         <v>0.0154</v>
       </c>
       <c r="I8" t="n">
-        <v>1.456906975305248</v>
+        <v>1.414462700096888</v>
       </c>
       <c r="J8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K8" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08462501320973281</v>
+        <v>0.08041792084995336</v>
       </c>
       <c r="M8" t="n">
-        <v>26.98540316257864</v>
+        <v>26.98163890995291</v>
       </c>
       <c r="N8" t="n">
-        <v>1269.292377341219</v>
+        <v>1271.052704432716</v>
       </c>
       <c r="O8" t="n">
-        <v>35.62712979375716</v>
+        <v>35.65182610235716</v>
       </c>
       <c r="P8" t="n">
-        <v>286.064513529681</v>
+        <v>286.5304395744452</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21424,28 +21534,28 @@
         <v>0.0114</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06416754688195825</v>
+        <v>-0.05624071829056653</v>
       </c>
       <c r="J9" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004692776972826662</v>
+        <v>0.0003639029478867961</v>
       </c>
       <c r="M9" t="n">
-        <v>17.01276180748278</v>
+        <v>16.97829765623059</v>
       </c>
       <c r="N9" t="n">
-        <v>486.3419403478482</v>
+        <v>484.3902195575756</v>
       </c>
       <c r="O9" t="n">
-        <v>22.05316168597709</v>
+        <v>22.00886683947121</v>
       </c>
       <c r="P9" t="n">
-        <v>334.720469215685</v>
+        <v>334.6345836353509</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21496,28 +21606,28 @@
         <v>0.0157</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3244002402351487</v>
+        <v>0.2556519206801785</v>
       </c>
       <c r="J10" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K10" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01326496794598031</v>
+        <v>0.008157717614790005</v>
       </c>
       <c r="M10" t="n">
-        <v>15.38056538005561</v>
+        <v>15.65457499462534</v>
       </c>
       <c r="N10" t="n">
-        <v>434.823373762459</v>
+        <v>443.7209773040772</v>
       </c>
       <c r="O10" t="n">
-        <v>20.85241889475796</v>
+        <v>21.06468554961306</v>
       </c>
       <c r="P10" t="n">
-        <v>291.3895094540683</v>
+        <v>292.13466752728</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21568,28 +21678,28 @@
         <v>0.0103</v>
       </c>
       <c r="I11" t="n">
-        <v>3.581059591551641</v>
+        <v>3.568115409783069</v>
       </c>
       <c r="J11" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K11" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3249729124002909</v>
+        <v>0.3256793231326879</v>
       </c>
       <c r="M11" t="n">
-        <v>31.10184933287506</v>
+        <v>30.97282675946067</v>
       </c>
       <c r="N11" t="n">
-        <v>1455.04809702444</v>
+        <v>1447.44229393545</v>
       </c>
       <c r="O11" t="n">
-        <v>38.14509269911976</v>
+        <v>38.04526638013525</v>
       </c>
       <c r="P11" t="n">
-        <v>294.9762091663259</v>
+        <v>295.1190374995886</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21640,28 +21750,28 @@
         <v>0.0174</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1772893591757536</v>
+        <v>-0.1828816170393852</v>
       </c>
       <c r="J12" t="n">
+        <v>366</v>
+      </c>
+      <c r="K12" t="n">
         <v>364</v>
       </c>
-      <c r="K12" t="n">
-        <v>362</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.004065757625929312</v>
+        <v>0.004369673182608169</v>
       </c>
       <c r="M12" t="n">
-        <v>14.89783135499654</v>
+        <v>14.85603838630688</v>
       </c>
       <c r="N12" t="n">
-        <v>439.247470309985</v>
+        <v>437.0034260411988</v>
       </c>
       <c r="O12" t="n">
-        <v>20.95823156447092</v>
+        <v>20.90462690509445</v>
       </c>
       <c r="P12" t="n">
-        <v>293.7694202230308</v>
+        <v>293.8289429249521</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21699,7 +21809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M365"/>
+  <dimension ref="A1:M367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45833,17 +45943,17 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>-36.94641299221073,175.1701031096184</t>
+          <t>-36.94645408407542,175.17012745785067</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>-36.94562212792744,175.17062896003677</t>
+          <t>-36.94563653038691,175.17063749396993</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>-36.94581952147836,175.17138906768113</t>
+          <t>-36.945977397663626,175.171564361237</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -45900,17 +46010,17 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>-36.94641299221073,175.1701031096184</t>
+          <t>-36.94645408407542,175.17012745785067</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>-36.94562082601017,175.17062818860794</t>
+          <t>-36.94563653038691,175.17063749396993</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>-36.94569413516042,175.1712498491163</t>
+          <t>-36.945977397663626,175.171564361237</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
@@ -45924,6 +46034,140 @@
         </is>
       </c>
       <c r="M365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-36.9471151160475,175.1658264869589</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-36.94774478252965,175.16631033738884</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-36.94783621759914,175.1671792351589</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-36.94771365512498,175.16806666079688</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-36.94756982854885,175.1688044354015</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-36.94690600252985,175.16941278279944</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-36.94645408407542,175.17012745785067</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-36.94563653038691,175.17063749396993</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-36.945977397663626,175.171564361237</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-36.94552042398373,175.17053806670208</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-36.94504547104793,175.17167063137464</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-36.947105586316276,175.16583026897914</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-36.94775532071686,175.16631069710277</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-36.94782465798982,175.167177720233</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-36.947702632093225,175.16806522921692</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-36.947559757840004,175.16879867069576</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-36.94694251897408,175.16943368581724</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-36.94649306031371,175.17015055253552</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-36.945818717365796,175.1707454461006</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-36.94599286911075,175.17158153959645</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-36.94552042398373,175.17053806670208</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-36.945046727546654,175.17168525351795</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
